--- a/distances.xlsx
+++ b/distances.xlsx
@@ -524,7 +524,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Zone de ressuage/ FPI</t>
+          <t>Zone de ressuage/ FPI  1</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
@@ -715,7 +715,7 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Zone de ressuage/ FPI</t>
+          <t>Zone de ressuage/ FPI  1</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Zone de ressuage/ FPI (copie)</t>
+          <t>Zone de ressuage/ FPI  2</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
@@ -855,7 +855,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Zone de ressuage/ FPI (copie)</t>
+          <t>Zone de ressuage/ FPI  2</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>64.11</v>
+        <v>63.556</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>1</v>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Zone de ressuage/ FPI (copie)</t>
+          <t>Zone de ressuage/ FPI  2</t>
         </is>
       </c>
       <c r="C23" s="4" t="n">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Zone de ressuage/ FPI (copie)</t>
+          <t>Zone de ressuage/ FPI  2</t>
         </is>
       </c>
       <c r="C25" s="4" t="n">
@@ -1368,7 +1368,7 @@
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>63.863</v>
+        <v>63.447</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>1</v>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Zone de ressuage/ FPI (copie)</t>
+          <t>Zone de ressuage/ FPI  2</t>
         </is>
       </c>
       <c r="C33" s="4" t="n">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Zone de ressuage/ FPI</t>
+          <t>Zone de ressuage/ FPI  1</t>
         </is>
       </c>
       <c r="C35" s="4" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Zone de ressuage/ FPI</t>
+          <t>Zone de ressuage/ FPI  1</t>
         </is>
       </c>
       <c r="C41" s="4" t="n">
@@ -1695,7 +1695,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Zone de ressuage/ FPI (copie)</t>
+          <t>Zone de ressuage/ FPI  2</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Zone de ressuage/ FPI</t>
+          <t>Zone de ressuage/ FPI  1</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
